--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260709.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260709.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>915,244,000</t>
+          <t>921,244,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.65%</t>
+          <t>10.56%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>169,841,000</t>
+          <t>171,041,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.45%</t>
+          <t>10.47%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.00%</t>
+          <t>5.92%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.93%</t>
+          <t>4.74%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.59%</t>
+          <t>3.58%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.55%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.44%</t>
         </is>
       </c>
     </row>
@@ -792,227 +792,227 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.22%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>31,536,000</t>
+          <t>25,944,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>97,242,442</t>
+          <t>31,886,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.83%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>202607TX</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>134,019,945</t>
+          <t>1,857</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.78%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>25,944,000</t>
+          <t>97,242,442</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>226,166,516</t>
+          <t>134,019,945</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.74%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>343,589,964</t>
+          <t>28,430,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.74%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>28,430,000</t>
+          <t>343,589,964</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.63%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>202607TX</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>1,670</t>
+          <t>226,166,516</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.53%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>134,528,000</t>
+          <t>191,517,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>191,517,000</t>
+          <t>134,528,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.39%</t>
         </is>
       </c>
     </row>
@@ -1034,51 +1034,51 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.37%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>101,917,000</t>
+          <t>150,152,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>150,152,000</t>
+          <t>101,917,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.23%</t>
         </is>
       </c>
     </row>
@@ -1107,61 +1107,61 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>51,717,000</t>
+          <t>181,756,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>82,168,000</t>
+          <t>51,717,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>2.04%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>179,956,000</t>
+          <t>82,168,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.70%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.60%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>10,876,151,059</t>
+          <t>10,851,722,040</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>3,225,656,085</t>
+          <t>3,256,101,821</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-66,515,215</t>
+          <t>-182,459,833</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
